--- a/Result/profitability/2615.xlsx
+++ b/Result/profitability/2615.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1275</v>
+        <v>2.82</v>
       </c>
       <c r="N2" t="n">
-        <v>28.725</v>
+        <v>26.4175</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.54</v>
       </c>
       <c r="M3" t="n">
-        <v>2.37375</v>
+        <v>2.3175</v>
       </c>
       <c r="N3" t="n">
-        <v>23.93375</v>
+        <v>23.505</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8425</v>
+        <v>1.967500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>20.32125</v>
+        <v>20.445</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.78</v>
       </c>
       <c r="M5" t="n">
-        <v>1.356250000000001</v>
+        <v>1.8225</v>
       </c>
       <c r="N5" t="n">
-        <v>16.98</v>
+        <v>17.225</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3</v>
+        <v>1.295</v>
       </c>
       <c r="N6" t="n">
-        <v>12.935</v>
+        <v>12.90125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7187500000000004</v>
+        <v>0.7862500000000004</v>
       </c>
       <c r="N7" t="n">
-        <v>9.856249999999999</v>
+        <v>10.6625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.63</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1937500000000004</v>
+        <v>0.3662500000000005</v>
       </c>
       <c r="N8" t="n">
-        <v>7.92875</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,10 +1645,10 @@
         <v>-0.02</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.09124999999999955</v>
+        <v>-0.09124999999999954</v>
       </c>
       <c r="N10" t="n">
-        <v>6.65</v>
+        <v>6.649999999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.05874999999999955</v>
       </c>
       <c r="N11" t="n">
-        <v>8.185</v>
+        <v>8.184999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07875000000000043</v>
+        <v>0.07875000000000046</v>
       </c>
       <c r="N12" t="n">
         <v>10.74375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>42900</v>
+      </c>
+      <c r="D75" t="n">
+        <v>29870</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13031</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>11133</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>25.95%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4979</v>
+      </c>
+      <c r="J75" t="n">
+        <v>16112</v>
+      </c>
+      <c r="K75" t="n">
+        <v>11535</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.6475</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.01375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5054945054945057</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7.609999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3343585237258349</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>9.815789473684211</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.960000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.06898979232664559</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
